--- a/data/excel/fingate_AccountDetail.xlsx
+++ b/data/excel/fingate_AccountDetail.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lalup\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iitracin-my.sharepoint.com/personal/laluprasad_r_mfs_iitr_ac_in/Documents/Desktop/nl2sql/data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF6C4BA2-9CCD-4968-85F4-1CD7549160BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{CF6C4BA2-9CCD-4968-85F4-1CD7549160BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D56D43E4-42E9-42AE-AC41-00FD34F0418A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{836BB986-0240-430F-947A-4AB1B81F7B92}"/>
   </bookViews>
@@ -3437,6 +3437,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F97DCF78-AA05-4668-AF86-7E9221BF7DCE}">
   <dimension ref="A1:AD101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="16" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -3781,7 +3789,7 @@
         <v>20085</v>
       </c>
       <c r="B5" s="4">
-        <v>6712</v>
+        <v>7970</v>
       </c>
       <c r="C5" s="4">
         <v>40</v>
@@ -3863,7 +3871,7 @@
         <v>27424</v>
       </c>
       <c r="B6" s="2">
-        <v>2106</v>
+        <v>7972</v>
       </c>
       <c r="C6" s="2">
         <v>10</v>
